--- a/game_theo_chu_de.xlsx
+++ b/game_theo_chu_de.xlsx
@@ -1,14 +1,30 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Game theo chủ đề" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>SheetJS</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Game theo chủ đề</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"/>
+</file>
+
+<file path=xl\metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -30,7 +46,7 @@
 </metadata>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -75,7 +91,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -395,7 +411,16 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="Game theo chủ đề" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I315"/>
   <cols>
@@ -441,10 +466,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cảm xúc &amp; Thái độ</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B2" t="str">
-        <v>爱</v>
+        <v>爸爸</v>
       </c>
       <c r="C2" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -470,10 +495,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cảm xúc &amp; Thái độ</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B3" t="str">
-        <v>高兴</v>
+        <v>大家</v>
       </c>
       <c r="C3" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -499,10 +524,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cảm xúc &amp; Thái độ</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B4" t="str">
-        <v>觉得</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -528,10 +553,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cảm xúc &amp; Thái độ</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B5" t="str">
-        <v>喜欢</v>
+        <v>对不起</v>
       </c>
       <c r="C5" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -557,10 +582,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B6" t="str">
-        <v>八</v>
+        <v>儿子</v>
       </c>
       <c r="C6" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -581,15 +606,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I6" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B7" t="str">
-        <v>百</v>
+        <v>哥哥</v>
       </c>
       <c r="C7" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -610,15 +635,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I7" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B8" t="str">
-        <v>半</v>
+        <v>孩子</v>
       </c>
       <c r="C8" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -639,15 +664,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I8" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B9" t="str">
-        <v>本</v>
+        <v>家人</v>
       </c>
       <c r="C9" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -668,15 +693,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I9" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B10" t="str">
-        <v>第</v>
+        <v>接</v>
       </c>
       <c r="C10" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -697,15 +722,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I10" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B11" t="str">
-        <v>多少</v>
+        <v>姐姐</v>
       </c>
       <c r="C11" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -726,15 +751,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I11" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B12" t="str">
-        <v>二</v>
+        <v>妈妈</v>
       </c>
       <c r="C12" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -755,15 +780,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I12" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B13" t="str">
-        <v>个</v>
+        <v>妹妹</v>
       </c>
       <c r="C13" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -784,15 +809,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I13" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B14" t="str">
-        <v>号</v>
+        <v>们</v>
       </c>
       <c r="C14" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -813,15 +838,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I14" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B15" t="str">
-        <v>几</v>
+        <v>名字</v>
       </c>
       <c r="C15" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -842,15 +867,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I15" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B16" t="str">
-        <v>斤</v>
+        <v>男</v>
       </c>
       <c r="C16" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -871,15 +896,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I16" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B17" t="str">
-        <v>九</v>
+        <v>男朋友</v>
       </c>
       <c r="C17" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -900,15 +925,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I17" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B18" t="str">
-        <v>口</v>
+        <v>你</v>
       </c>
       <c r="C18" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -929,15 +954,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I18" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B19" t="str">
-        <v>块</v>
+        <v>你们</v>
       </c>
       <c r="C19" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -958,15 +983,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I19" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B20" t="str">
-        <v>两</v>
+        <v>您</v>
       </c>
       <c r="C20" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -987,15 +1012,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I20" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B21" t="str">
-        <v>零</v>
+        <v>女</v>
       </c>
       <c r="C21" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1016,15 +1041,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I21" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B22" t="str">
-        <v>六</v>
+        <v>女儿</v>
       </c>
       <c r="C22" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1045,15 +1070,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I22" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B23" t="str">
-        <v>七</v>
+        <v>女朋友</v>
       </c>
       <c r="C23" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1074,15 +1099,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I23" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B24" t="str">
-        <v>千</v>
+        <v>女士</v>
       </c>
       <c r="C24" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1103,15 +1128,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I24" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B25" t="str">
-        <v>三</v>
+        <v>朋友</v>
       </c>
       <c r="C25" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1132,15 +1157,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I25" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B26" t="str">
-        <v>十</v>
+        <v>人</v>
       </c>
       <c r="C26" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1161,15 +1186,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I26" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B27" t="str">
-        <v>四</v>
+        <v>谁</v>
       </c>
       <c r="C27" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1190,15 +1215,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I27" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B28" t="str">
-        <v>岁</v>
+        <v>他</v>
       </c>
       <c r="C28" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1219,15 +1244,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I28" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B29" t="str">
-        <v>五</v>
+        <v>他们</v>
       </c>
       <c r="C29" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1248,15 +1273,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I29" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B30" t="str">
-        <v>些</v>
+        <v>它</v>
       </c>
       <c r="C30" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1277,15 +1302,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I30" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B31" t="str">
-        <v>一</v>
+        <v>它们</v>
       </c>
       <c r="C31" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1306,15 +1331,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I31" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B32" t="str">
-        <v>一半</v>
+        <v>她们</v>
       </c>
       <c r="C32" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1335,15 +1360,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I32" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B33" t="str">
-        <v>一下</v>
+        <v>同学</v>
       </c>
       <c r="C33" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1364,15 +1389,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I33" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B34" t="str">
-        <v>一点儿</v>
+        <v>我</v>
       </c>
       <c r="C34" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1393,15 +1418,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I34" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B35" t="str">
-        <v>一些</v>
+        <v>我们</v>
       </c>
       <c r="C35" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1422,15 +1447,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I35" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B36" t="str">
-        <v>有</v>
+        <v>先生</v>
       </c>
       <c r="C36" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1451,15 +1476,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I36" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B37" t="str">
-        <v>有的</v>
+        <v>小朋友</v>
       </c>
       <c r="C37" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1480,15 +1505,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I37" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Con người &amp; Các mối quan hệ</v>
       </c>
       <c r="B38" t="str">
-        <v>有点儿</v>
+        <v>她</v>
       </c>
       <c r="C38" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1509,15 +1534,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I38" t="str">
-        <v>game.html?topic=chude2</v>
+        <v>game.html?topic=chude1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Cơ thể &amp; Sức khỏe</v>
       </c>
       <c r="B39" t="str">
-        <v>有些</v>
+        <v>病</v>
       </c>
       <c r="C39" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1543,10 +1568,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Số lượng &amp; Đo lường</v>
+        <v>Cơ thể &amp; Sức khỏe</v>
       </c>
       <c r="B40" t="str">
-        <v>只</v>
+        <v>病人</v>
       </c>
       <c r="C40" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1572,10 +1597,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cơ thể &amp; Sức khỏe</v>
       </c>
       <c r="B41" t="str">
-        <v>爸爸</v>
+        <v>看病</v>
       </c>
       <c r="C41" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1596,15 +1621,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I41" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cơ thể &amp; Sức khỏe</v>
       </c>
       <c r="B42" t="str">
-        <v>大家</v>
+        <v>生病</v>
       </c>
       <c r="C42" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1625,15 +1650,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I42" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cơ thể &amp; Sức khỏe</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>药</v>
       </c>
       <c r="C43" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1654,15 +1679,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I43" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cảm xúc &amp; Thái độ</v>
       </c>
       <c r="B44" t="str">
-        <v>对不起</v>
+        <v>爱</v>
       </c>
       <c r="C44" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1688,10 +1713,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cảm xúc &amp; Thái độ</v>
       </c>
       <c r="B45" t="str">
-        <v>儿子</v>
+        <v>高兴</v>
       </c>
       <c r="C45" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1717,10 +1742,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cảm xúc &amp; Thái độ</v>
       </c>
       <c r="B46" t="str">
-        <v>哥哥</v>
+        <v>觉得</v>
       </c>
       <c r="C46" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1746,10 +1771,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Cảm xúc &amp; Thái độ</v>
       </c>
       <c r="B47" t="str">
-        <v>孩子</v>
+        <v>喜欢</v>
       </c>
       <c r="C47" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1775,10 +1800,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B48" t="str">
-        <v>家人</v>
+        <v>读</v>
       </c>
       <c r="C48" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1799,15 +1824,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I48" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B49" t="str">
-        <v>接</v>
+        <v>读书</v>
       </c>
       <c r="C49" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1828,15 +1853,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I49" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B50" t="str">
-        <v>姐姐</v>
+        <v>会</v>
       </c>
       <c r="C50" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1857,15 +1882,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I50" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B51" t="str">
-        <v>妈妈</v>
+        <v>见</v>
       </c>
       <c r="C51" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1886,15 +1911,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I51" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>叫</v>
       </c>
       <c r="C52" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1915,15 +1940,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I52" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B53" t="str">
-        <v>们</v>
+        <v>看</v>
       </c>
       <c r="C53" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1944,15 +1969,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I53" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B54" t="str">
-        <v>名字</v>
+        <v>看见</v>
       </c>
       <c r="C54" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -1973,15 +1998,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I54" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B55" t="str">
-        <v>男</v>
+        <v>请问</v>
       </c>
       <c r="C55" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2002,15 +2027,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I55" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B56" t="str">
-        <v>男朋友</v>
+        <v>认识</v>
       </c>
       <c r="C56" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2031,15 +2056,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I56" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B57" t="str">
-        <v>你</v>
+        <v>说</v>
       </c>
       <c r="C57" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2060,15 +2085,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I57" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B58" t="str">
-        <v>你们</v>
+        <v>说话</v>
       </c>
       <c r="C58" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2089,15 +2114,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I58" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B59" t="str">
-        <v>您</v>
+        <v>听</v>
       </c>
       <c r="C59" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2118,15 +2143,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I59" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B60" t="str">
-        <v>女</v>
+        <v>听见</v>
       </c>
       <c r="C60" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2147,15 +2172,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I60" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B61" t="str">
-        <v>女儿</v>
+        <v>问</v>
       </c>
       <c r="C61" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2176,15 +2201,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I61" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B62" t="str">
-        <v>女朋友</v>
+        <v>问题</v>
       </c>
       <c r="C62" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2205,15 +2230,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I62" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B63" t="str">
-        <v>女士</v>
+        <v>想</v>
       </c>
       <c r="C63" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2234,15 +2259,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I63" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B64" t="str">
-        <v>朋友</v>
+        <v>学</v>
       </c>
       <c r="C64" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2263,15 +2288,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I64" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B65" t="str">
-        <v>人</v>
+        <v>学习</v>
       </c>
       <c r="C65" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2292,15 +2317,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I65" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Tư duy &amp; Nhận thức</v>
       </c>
       <c r="B66" t="str">
-        <v>谁</v>
+        <v>知道</v>
       </c>
       <c r="C66" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2321,15 +2346,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I66" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B67" t="str">
-        <v>他</v>
+        <v>唱</v>
       </c>
       <c r="C67" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2350,15 +2375,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I67" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B68" t="str">
-        <v>他们</v>
+        <v>吃</v>
       </c>
       <c r="C68" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2379,15 +2404,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I68" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B69" t="str">
-        <v>它</v>
+        <v>穿</v>
       </c>
       <c r="C69" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2408,15 +2433,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I69" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B70" t="str">
-        <v>它们</v>
+        <v>打电话</v>
       </c>
       <c r="C70" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2437,15 +2462,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I70" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B71" t="str">
-        <v>她们</v>
+        <v>歌</v>
       </c>
       <c r="C71" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2466,15 +2491,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I71" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B72" t="str">
-        <v>同学</v>
+        <v>给</v>
       </c>
       <c r="C72" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2495,15 +2520,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I72" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B73" t="str">
-        <v>我</v>
+        <v>喝</v>
       </c>
       <c r="C73" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2524,15 +2549,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I73" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B74" t="str">
-        <v>我们</v>
+        <v>开</v>
       </c>
       <c r="C74" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2553,15 +2578,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I74" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B75" t="str">
-        <v>先生</v>
+        <v>买</v>
       </c>
       <c r="C75" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2582,15 +2607,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I75" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B76" t="str">
-        <v>小朋友</v>
+        <v>卖</v>
       </c>
       <c r="C76" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2611,15 +2636,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I76" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Con người &amp; Các mối quan hệ</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B77" t="str">
-        <v>她</v>
+        <v>起床</v>
       </c>
       <c r="C77" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2640,15 +2665,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I77" t="str">
-        <v>game.html?topic=chude3</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B78" t="str">
-        <v>吧</v>
+        <v>睡</v>
       </c>
       <c r="C78" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2669,15 +2694,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I78" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B79" t="str">
-        <v>不客气</v>
+        <v>睡觉</v>
       </c>
       <c r="C79" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2698,15 +2723,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I79" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B80" t="str">
-        <v>不要</v>
+        <v>玩</v>
       </c>
       <c r="C80" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2727,15 +2752,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I80" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B81" t="str">
-        <v>不</v>
+        <v>写</v>
       </c>
       <c r="C81" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2756,15 +2781,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I81" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B82" t="str">
-        <v>的</v>
+        <v>休息</v>
       </c>
       <c r="C82" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2785,15 +2810,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I82" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B83" t="str">
-        <v>都</v>
+        <v>找</v>
       </c>
       <c r="C83" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2814,15 +2839,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I83" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B84" t="str">
-        <v>还</v>
+        <v>住</v>
       </c>
       <c r="C84" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2843,15 +2868,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I84" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B85" t="str">
-        <v>和</v>
+        <v>做</v>
       </c>
       <c r="C85" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2872,15 +2897,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I85" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đời sống sinh hoạt</v>
       </c>
       <c r="B86" t="str">
-        <v>很</v>
+        <v>做饭</v>
       </c>
       <c r="C86" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2901,15 +2926,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I86" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B87" t="str">
-        <v>可以</v>
+        <v>杯</v>
       </c>
       <c r="C87" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2930,15 +2955,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I87" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B88" t="str">
-        <v>了</v>
+        <v>杯子</v>
       </c>
       <c r="C88" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2959,15 +2984,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I88" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B89" t="str">
-        <v>吗</v>
+        <v>电话</v>
       </c>
       <c r="C89" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -2988,15 +3013,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I89" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B90" t="str">
-        <v>没</v>
+        <v>电脑</v>
       </c>
       <c r="C90" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3017,15 +3042,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I90" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B91" t="str">
-        <v>没关系</v>
+        <v>电视</v>
       </c>
       <c r="C91" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3046,15 +3071,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I91" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B92" t="str">
-        <v>没事</v>
+        <v>电影</v>
       </c>
       <c r="C92" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3075,15 +3100,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I92" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B93" t="str">
-        <v>没有</v>
+        <v>东西</v>
       </c>
       <c r="C93" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3104,15 +3129,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I93" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B94" t="str">
-        <v>哪个</v>
+        <v>件</v>
       </c>
       <c r="C94" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3133,15 +3158,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I94" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B95" t="str">
-        <v>哪些</v>
+        <v>钱</v>
       </c>
       <c r="C95" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3162,15 +3187,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I95" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B96" t="str">
-        <v>那</v>
+        <v>事</v>
       </c>
       <c r="C96" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3191,15 +3216,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I96" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B97" t="str">
-        <v>那些</v>
+        <v>手机</v>
       </c>
       <c r="C97" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3220,15 +3245,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I97" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B98" t="str">
-        <v>呢</v>
+        <v>书</v>
       </c>
       <c r="C98" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3249,15 +3274,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I98" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B99" t="str">
-        <v>能</v>
+        <v>衣服</v>
       </c>
       <c r="C99" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3278,15 +3303,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I99" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B100" t="str">
-        <v>你好</v>
+        <v>椅子</v>
       </c>
       <c r="C100" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3307,15 +3332,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I100" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B101" t="str">
-        <v>请</v>
+        <v>元</v>
       </c>
       <c r="C101" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3336,15 +3361,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I101" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B102" t="str">
-        <v>什么</v>
+        <v>中文</v>
       </c>
       <c r="C102" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3365,15 +3390,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I102" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B103" t="str">
-        <v>是</v>
+        <v>桌子</v>
       </c>
       <c r="C103" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3394,15 +3419,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I103" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B104" t="str">
-        <v>太</v>
+        <v>字</v>
       </c>
       <c r="C104" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3423,15 +3448,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I104" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B105" t="str">
-        <v>喂</v>
+        <v>汉语</v>
       </c>
       <c r="C105" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3452,15 +3477,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I105" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Đồ vật &amp; Công cụ</v>
       </c>
       <c r="B106" t="str">
-        <v>谢谢</v>
+        <v>汉字</v>
       </c>
       <c r="C106" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3481,15 +3506,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I106" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B107" t="str">
-        <v>要</v>
+        <v>超市</v>
       </c>
       <c r="C107" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3510,15 +3535,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I107" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B108" t="str">
-        <v>也</v>
+        <v>大学</v>
       </c>
       <c r="C108" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3539,15 +3564,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I108" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B109" t="str">
-        <v>再</v>
+        <v>电影院</v>
       </c>
       <c r="C109" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3568,15 +3593,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I109" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B110" t="str">
-        <v>再见</v>
+        <v>店</v>
       </c>
       <c r="C110" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3597,15 +3622,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I110" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B111" t="str">
-        <v>在</v>
+        <v>饭店</v>
       </c>
       <c r="C111" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3626,15 +3651,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I111" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B112" t="str">
-        <v>怎么</v>
+        <v>房间</v>
       </c>
       <c r="C112" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3655,15 +3680,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I112" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B113" t="str">
-        <v>怎么样</v>
+        <v>公司</v>
       </c>
       <c r="C113" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3684,15 +3709,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I113" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B114" t="str">
-        <v>这</v>
+        <v>国</v>
       </c>
       <c r="C114" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3713,15 +3738,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I114" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B115" t="str">
-        <v>这些</v>
+        <v>机场</v>
       </c>
       <c r="C115" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3742,15 +3767,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I115" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B116" t="str">
-        <v>正在</v>
+        <v>家</v>
       </c>
       <c r="C116" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3771,15 +3796,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I116" t="str">
-        <v>game.html?topic=chude4</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B117" t="str">
-        <v>白天</v>
+        <v>哪</v>
       </c>
       <c r="C117" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3800,15 +3825,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I117" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B118" t="str">
-        <v>点</v>
+        <v>哪儿</v>
       </c>
       <c r="C118" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3829,15 +3854,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I118" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B119" t="str">
-        <v>分</v>
+        <v>那里</v>
       </c>
       <c r="C119" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3858,15 +3883,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I119" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B120" t="str">
-        <v>分钟</v>
+        <v>那儿</v>
       </c>
       <c r="C120" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3887,15 +3912,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I120" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B121" t="str">
-        <v>今年</v>
+        <v>商店</v>
       </c>
       <c r="C121" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3916,15 +3941,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I121" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B122" t="str">
-        <v>今天</v>
+        <v>书店</v>
       </c>
       <c r="C122" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3945,15 +3970,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I122" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B123" t="str">
-        <v>明年</v>
+        <v>小学</v>
       </c>
       <c r="C123" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -3974,15 +3999,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I123" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B124" t="str">
-        <v>明天</v>
+        <v>学校</v>
       </c>
       <c r="C124" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4003,15 +4028,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I124" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B125" t="str">
-        <v>年</v>
+        <v>医院</v>
       </c>
       <c r="C125" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4032,15 +4057,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I125" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B126" t="str">
-        <v>去年</v>
+        <v>中国</v>
       </c>
       <c r="C126" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4061,15 +4086,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I126" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B127" t="str">
-        <v>日</v>
+        <v>法国</v>
       </c>
       <c r="C127" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4090,15 +4115,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I127" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B128" t="str">
-        <v>上午</v>
+        <v>泰国</v>
       </c>
       <c r="C128" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4119,15 +4144,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I128" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B129" t="str">
-        <v>时候</v>
+        <v>这里</v>
       </c>
       <c r="C129" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4148,15 +4173,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I129" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B130" t="str">
-        <v>时间</v>
+        <v>这儿</v>
       </c>
       <c r="C130" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4177,15 +4202,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I130" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B131" t="str">
-        <v>晚</v>
+        <v>中学</v>
       </c>
       <c r="C131" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4206,15 +4231,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I131" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B132" t="str">
-        <v>晚上</v>
+        <v>西安</v>
       </c>
       <c r="C132" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4235,15 +4260,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I132" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Thời gian</v>
+        <v>Địa điểm &amp; Nơi chốn</v>
       </c>
       <c r="B133" t="str">
-        <v>下午</v>
+        <v>北京</v>
       </c>
       <c r="C133" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4264,15 +4289,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I133" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B134" t="str">
-        <v>现在</v>
+        <v>车</v>
       </c>
       <c r="C134" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4293,15 +4318,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I134" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B135" t="str">
-        <v>小时</v>
+        <v>出租车</v>
       </c>
       <c r="C135" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4322,15 +4347,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I135" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B136" t="str">
-        <v>星期</v>
+        <v>到</v>
       </c>
       <c r="C136" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4351,15 +4376,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I136" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B137" t="str">
-        <v>星期日</v>
+        <v>飞机</v>
       </c>
       <c r="C137" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4380,15 +4405,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I137" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B138" t="str">
-        <v>星期天</v>
+        <v>回</v>
       </c>
       <c r="C138" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4409,15 +4434,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I138" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B139" t="str">
-        <v>月</v>
+        <v>火车</v>
       </c>
       <c r="C139" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4438,15 +4463,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I139" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B140" t="str">
-        <v>早</v>
+        <v>开车</v>
       </c>
       <c r="C140" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4467,15 +4492,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I140" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B141" t="str">
-        <v>中午</v>
+        <v>来</v>
       </c>
       <c r="C141" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4496,15 +4521,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I141" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Thời gian</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B142" t="str">
-        <v>昨天</v>
+        <v>去</v>
       </c>
       <c r="C142" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4525,15 +4550,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I142" t="str">
-        <v>game.html?topic=chude5</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Giao thông &amp; Di chuyển</v>
       </c>
       <c r="B143" t="str">
-        <v>包子</v>
+        <v>坐</v>
       </c>
       <c r="C143" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4554,15 +4579,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I143" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude8</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B144" t="str">
-        <v>菜</v>
+        <v>边</v>
       </c>
       <c r="C144" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4583,15 +4608,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I144" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B145" t="str">
-        <v>茶</v>
+        <v>后</v>
       </c>
       <c r="C145" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4612,15 +4637,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I145" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B146" t="str">
-        <v>饭</v>
+        <v>里</v>
       </c>
       <c r="C146" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4641,15 +4666,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I146" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B147" t="str">
-        <v>好吃</v>
+        <v>哪里</v>
       </c>
       <c r="C147" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4670,15 +4695,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I147" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B148" t="str">
-        <v>鸡蛋</v>
+        <v>那边</v>
       </c>
       <c r="C148" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4699,15 +4724,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I148" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B149" t="str">
-        <v>饺子</v>
+        <v>那个</v>
       </c>
       <c r="C149" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4728,15 +4753,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I149" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B150" t="str">
-        <v>米饭</v>
+        <v>前</v>
       </c>
       <c r="C150" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4757,15 +4782,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I150" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B151" t="str">
-        <v>面包</v>
+        <v>前边</v>
       </c>
       <c r="C151" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4786,15 +4811,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I151" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B152" t="str">
-        <v>面条儿</v>
+        <v>上</v>
       </c>
       <c r="C152" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4815,15 +4840,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I152" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B153" t="str">
-        <v>牛奶</v>
+        <v>外</v>
       </c>
       <c r="C153" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4844,15 +4869,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I153" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B154" t="str">
-        <v>苹果</v>
+        <v>外边</v>
       </c>
       <c r="C154" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4873,15 +4898,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I154" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B155" t="str">
-        <v>水果</v>
+        <v>下</v>
       </c>
       <c r="C155" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4902,15 +4927,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I155" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B156" t="str">
-        <v>晚饭</v>
+        <v>这边</v>
       </c>
       <c r="C156" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4931,15 +4956,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I156" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Không gian &amp; Vị trí</v>
       </c>
       <c r="B157" t="str">
-        <v>午饭</v>
+        <v>这个</v>
       </c>
       <c r="C157" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4960,15 +4985,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I157" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Đồ ăn &amp; Thức uống</v>
+        <v>Thời gian</v>
       </c>
       <c r="B158" t="str">
-        <v>早饭</v>
+        <v>白天</v>
       </c>
       <c r="C158" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -4989,15 +5014,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I158" t="str">
-        <v>game.html?topic=chude6</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B159" t="str">
-        <v>杯</v>
+        <v>点</v>
       </c>
       <c r="C159" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5018,15 +5043,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I159" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B160" t="str">
-        <v>杯子</v>
+        <v>分</v>
       </c>
       <c r="C160" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5047,15 +5072,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I160" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B161" t="str">
-        <v>电话</v>
+        <v>分钟</v>
       </c>
       <c r="C161" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5076,15 +5101,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I161" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B162" t="str">
-        <v>电脑</v>
+        <v>今年</v>
       </c>
       <c r="C162" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5105,15 +5130,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I162" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B163" t="str">
-        <v>电视</v>
+        <v>今天</v>
       </c>
       <c r="C163" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5134,15 +5159,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I163" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B164" t="str">
-        <v>电影</v>
+        <v>明年</v>
       </c>
       <c r="C164" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5163,15 +5188,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I164" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B165" t="str">
-        <v>东西</v>
+        <v>明天</v>
       </c>
       <c r="C165" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5192,15 +5217,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I165" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B166" t="str">
-        <v>件</v>
+        <v>年</v>
       </c>
       <c r="C166" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5221,15 +5246,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I166" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B167" t="str">
-        <v>钱</v>
+        <v>去年</v>
       </c>
       <c r="C167" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5250,15 +5275,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I167" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B168" t="str">
-        <v>事</v>
+        <v>日</v>
       </c>
       <c r="C168" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5279,15 +5304,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I168" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B169" t="str">
-        <v>手机</v>
+        <v>上午</v>
       </c>
       <c r="C169" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5308,15 +5333,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I169" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B170" t="str">
-        <v>书</v>
+        <v>时候</v>
       </c>
       <c r="C170" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5337,15 +5362,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I170" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B171" t="str">
-        <v>衣服</v>
+        <v>时间</v>
       </c>
       <c r="C171" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5366,15 +5391,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I171" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B172" t="str">
-        <v>椅子</v>
+        <v>晚</v>
       </c>
       <c r="C172" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5395,15 +5420,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I172" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B173" t="str">
-        <v>元</v>
+        <v>晚上</v>
       </c>
       <c r="C173" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5424,15 +5449,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I173" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B174" t="str">
-        <v>中文</v>
+        <v>下午</v>
       </c>
       <c r="C174" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5453,15 +5478,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I174" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B175" t="str">
-        <v>桌子</v>
+        <v>现在</v>
       </c>
       <c r="C175" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5482,15 +5507,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I175" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B176" t="str">
-        <v>字</v>
+        <v>小时</v>
       </c>
       <c r="C176" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5511,15 +5536,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I176" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B177" t="str">
-        <v>汉语</v>
+        <v>星期</v>
       </c>
       <c r="C177" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5540,15 +5565,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I177" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Đồ vật &amp; Công cụ</v>
+        <v>Thời gian</v>
       </c>
       <c r="B178" t="str">
-        <v>汉字</v>
+        <v>星期日</v>
       </c>
       <c r="C178" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5569,15 +5594,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I178" t="str">
-        <v>game.html?topic=chude7</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Thời gian</v>
       </c>
       <c r="B179" t="str">
-        <v>边</v>
+        <v>星期天</v>
       </c>
       <c r="C179" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5598,15 +5623,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I179" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Thời gian</v>
       </c>
       <c r="B180" t="str">
-        <v>后</v>
+        <v>月</v>
       </c>
       <c r="C180" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5627,15 +5652,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I180" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Thời gian</v>
       </c>
       <c r="B181" t="str">
-        <v>里</v>
+        <v>早</v>
       </c>
       <c r="C181" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5656,15 +5681,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I181" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Thời gian</v>
       </c>
       <c r="B182" t="str">
-        <v>哪里</v>
+        <v>中午</v>
       </c>
       <c r="C182" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5685,15 +5710,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I182" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Thời gian</v>
       </c>
       <c r="B183" t="str">
-        <v>那边</v>
+        <v>昨天</v>
       </c>
       <c r="C183" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5714,15 +5739,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I183" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude10</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B184" t="str">
-        <v>那个</v>
+        <v>大学生</v>
       </c>
       <c r="C184" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5743,15 +5768,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I184" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B185" t="str">
-        <v>前</v>
+        <v>服务员</v>
       </c>
       <c r="C185" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5772,15 +5797,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I185" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B186" t="str">
-        <v>前边</v>
+        <v>工作</v>
       </c>
       <c r="C186" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5801,15 +5826,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I186" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B187" t="str">
-        <v>上</v>
+        <v>老师</v>
       </c>
       <c r="C187" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5830,15 +5855,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I187" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B188" t="str">
-        <v>外</v>
+        <v>上班</v>
       </c>
       <c r="C188" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5859,15 +5884,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I188" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B189" t="str">
-        <v>外边</v>
+        <v>上课</v>
       </c>
       <c r="C189" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5888,15 +5913,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I189" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B190" t="str">
-        <v>下</v>
+        <v>上学</v>
       </c>
       <c r="C190" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5917,15 +5942,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I190" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B191" t="str">
-        <v>这边</v>
+        <v>售货员</v>
       </c>
       <c r="C191" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5946,15 +5971,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I191" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Không gian &amp; Vị trí</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B192" t="str">
-        <v>这个</v>
+        <v>下班</v>
       </c>
       <c r="C192" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -5975,15 +6000,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I192" t="str">
-        <v>game.html?topic=chude8</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Cơ thể &amp; Sức khỏe</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B193" t="str">
-        <v>病</v>
+        <v>下课</v>
       </c>
       <c r="C193" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6004,15 +6029,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I193" t="str">
-        <v>game.html?topic=chude9</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Cơ thể &amp; Sức khỏe</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B194" t="str">
-        <v>病人</v>
+        <v>小学生</v>
       </c>
       <c r="C194" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6033,15 +6058,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I194" t="str">
-        <v>game.html?topic=chude9</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Cơ thể &amp; Sức khỏe</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B195" t="str">
-        <v>看病</v>
+        <v>学生</v>
       </c>
       <c r="C195" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6062,15 +6087,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I195" t="str">
-        <v>game.html?topic=chude9</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Cơ thể &amp; Sức khỏe</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B196" t="str">
-        <v>生病</v>
+        <v>医</v>
       </c>
       <c r="C196" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6091,15 +6116,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I196" t="str">
-        <v>game.html?topic=chude9</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Cơ thể &amp; Sức khỏe</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B197" t="str">
-        <v>药</v>
+        <v>医生</v>
       </c>
       <c r="C197" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6120,15 +6145,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I197" t="str">
-        <v>game.html?topic=chude9</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Công việc &amp; Nghề nghiệp</v>
       </c>
       <c r="B198" t="str">
-        <v>唱</v>
+        <v>中学生</v>
       </c>
       <c r="C198" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6149,15 +6174,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I198" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude11</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B199" t="str">
-        <v>吃</v>
+        <v>大</v>
       </c>
       <c r="C199" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6178,15 +6203,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I199" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B200" t="str">
-        <v>穿</v>
+        <v>对</v>
       </c>
       <c r="C200" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6207,15 +6232,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I200" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B201" t="str">
-        <v>打电话</v>
+        <v>多</v>
       </c>
       <c r="C201" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6236,15 +6261,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I201" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B202" t="str">
-        <v>歌</v>
+        <v>非常</v>
       </c>
       <c r="C202" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6265,15 +6290,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I202" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B203" t="str">
-        <v>给</v>
+        <v>贵</v>
       </c>
       <c r="C203" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6294,15 +6319,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I203" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B204" t="str">
-        <v>喝</v>
+        <v>好</v>
       </c>
       <c r="C204" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6323,15 +6348,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I204" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B205" t="str">
-        <v>开</v>
+        <v>好看</v>
       </c>
       <c r="C205" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6352,15 +6377,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I205" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B206" t="str">
-        <v>买</v>
+        <v>好听</v>
       </c>
       <c r="C206" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6381,15 +6406,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I206" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B207" t="str">
-        <v>卖</v>
+        <v>好玩儿</v>
       </c>
       <c r="C207" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6410,15 +6435,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I207" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B208" t="str">
-        <v>起床</v>
+        <v>冷</v>
       </c>
       <c r="C208" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6439,15 +6464,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I208" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B209" t="str">
-        <v>睡</v>
+        <v>忙</v>
       </c>
       <c r="C209" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6468,15 +6493,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I209" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B210" t="str">
-        <v>睡觉</v>
+        <v>便宜</v>
       </c>
       <c r="C210" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6497,15 +6522,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I210" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B211" t="str">
-        <v>玩</v>
+        <v>漂亮</v>
       </c>
       <c r="C211" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6526,15 +6551,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I211" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B212" t="str">
-        <v>写</v>
+        <v>热</v>
       </c>
       <c r="C212" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6555,15 +6580,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I212" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B213" t="str">
-        <v>休息</v>
+        <v>少</v>
       </c>
       <c r="C213" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6584,15 +6609,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I213" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B214" t="str">
-        <v>找</v>
+        <v>小</v>
       </c>
       <c r="C214" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6613,15 +6638,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I214" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B215" t="str">
-        <v>住</v>
+        <v>新</v>
       </c>
       <c r="C215" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6642,15 +6667,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I215" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Miêu tả &amp; Đánh giá</v>
       </c>
       <c r="B216" t="str">
-        <v>做</v>
+        <v>真</v>
       </c>
       <c r="C216" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6671,15 +6696,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I216" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude12</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Đời sống sinh hoạt</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B217" t="str">
-        <v>做饭</v>
+        <v>八</v>
       </c>
       <c r="C217" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6700,15 +6725,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I217" t="str">
-        <v>game.html?topic=chude10</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B218" t="str">
-        <v>超市</v>
+        <v>百</v>
       </c>
       <c r="C218" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6729,15 +6754,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I218" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B219" t="str">
-        <v>大学</v>
+        <v>半</v>
       </c>
       <c r="C219" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6758,15 +6783,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I219" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B220" t="str">
-        <v>电影院</v>
+        <v>本</v>
       </c>
       <c r="C220" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6787,15 +6812,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I220" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B221" t="str">
-        <v>店</v>
+        <v>第</v>
       </c>
       <c r="C221" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6816,15 +6841,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I221" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B222" t="str">
-        <v>饭店</v>
+        <v>多少</v>
       </c>
       <c r="C222" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6845,15 +6870,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I222" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B223" t="str">
-        <v>房间</v>
+        <v>二</v>
       </c>
       <c r="C223" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6874,15 +6899,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I223" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B224" t="str">
-        <v>公司</v>
+        <v>个</v>
       </c>
       <c r="C224" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6903,15 +6928,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I224" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B225" t="str">
-        <v>国</v>
+        <v>号</v>
       </c>
       <c r="C225" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6932,15 +6957,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I225" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B226" t="str">
-        <v>机场</v>
+        <v>几</v>
       </c>
       <c r="C226" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6961,15 +6986,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I226" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B227" t="str">
-        <v>家</v>
+        <v>斤</v>
       </c>
       <c r="C227" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -6990,15 +7015,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I227" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B228" t="str">
-        <v>哪</v>
+        <v>九</v>
       </c>
       <c r="C228" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7019,15 +7044,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I228" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B229" t="str">
-        <v>哪儿</v>
+        <v>口</v>
       </c>
       <c r="C229" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7048,15 +7073,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I229" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B230" t="str">
-        <v>那里</v>
+        <v>块</v>
       </c>
       <c r="C230" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7077,15 +7102,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I230" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B231" t="str">
-        <v>那儿</v>
+        <v>两</v>
       </c>
       <c r="C231" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7106,15 +7131,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I231" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B232" t="str">
-        <v>商店</v>
+        <v>零</v>
       </c>
       <c r="C232" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7135,15 +7160,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I232" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B233" t="str">
-        <v>书店</v>
+        <v>六</v>
       </c>
       <c r="C233" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7164,15 +7189,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I233" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B234" t="str">
-        <v>小学</v>
+        <v>七</v>
       </c>
       <c r="C234" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7193,15 +7218,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I234" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B235" t="str">
-        <v>学校</v>
+        <v>千</v>
       </c>
       <c r="C235" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7222,15 +7247,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I235" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B236" t="str">
-        <v>医院</v>
+        <v>三</v>
       </c>
       <c r="C236" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7251,15 +7276,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I236" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B237" t="str">
-        <v>中国</v>
+        <v>十</v>
       </c>
       <c r="C237" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7280,15 +7305,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I237" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B238" t="str">
-        <v>法国</v>
+        <v>四</v>
       </c>
       <c r="C238" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7309,15 +7334,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I238" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B239" t="str">
-        <v>泰国</v>
+        <v>岁</v>
       </c>
       <c r="C239" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7338,15 +7363,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I239" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B240" t="str">
-        <v>这里</v>
+        <v>五</v>
       </c>
       <c r="C240" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7367,15 +7392,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I240" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B241" t="str">
-        <v>这儿</v>
+        <v>些</v>
       </c>
       <c r="C241" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7396,15 +7421,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I241" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B242" t="str">
-        <v>中学</v>
+        <v>一</v>
       </c>
       <c r="C242" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7425,15 +7450,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I242" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B243" t="str">
-        <v>西安</v>
+        <v>一半</v>
       </c>
       <c r="C243" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7454,15 +7479,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I243" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Địa điểm &amp; Nơi chốn</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B244" t="str">
-        <v>北京</v>
+        <v>一下</v>
       </c>
       <c r="C244" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7483,15 +7508,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I244" t="str">
-        <v>game.html?topic=chude11</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B245" t="str">
-        <v>车</v>
+        <v>一点儿</v>
       </c>
       <c r="C245" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7512,15 +7537,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I245" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B246" t="str">
-        <v>出租车</v>
+        <v>一些</v>
       </c>
       <c r="C246" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7541,15 +7566,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I246" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B247" t="str">
-        <v>到</v>
+        <v>有</v>
       </c>
       <c r="C247" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7570,15 +7595,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I247" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B248" t="str">
-        <v>飞机</v>
+        <v>有的</v>
       </c>
       <c r="C248" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7599,15 +7624,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I248" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B249" t="str">
-        <v>回</v>
+        <v>有点儿</v>
       </c>
       <c r="C249" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7628,15 +7653,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I249" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B250" t="str">
-        <v>火车</v>
+        <v>有些</v>
       </c>
       <c r="C250" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7657,15 +7682,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I250" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Số lượng &amp; Đo lường</v>
       </c>
       <c r="B251" t="str">
-        <v>开车</v>
+        <v>只</v>
       </c>
       <c r="C251" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7686,15 +7711,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I251" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude13</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B252" t="str">
-        <v>来</v>
+        <v>吧</v>
       </c>
       <c r="C252" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7715,15 +7740,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I252" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B253" t="str">
-        <v>去</v>
+        <v>不客气</v>
       </c>
       <c r="C253" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7744,15 +7769,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I253" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Giao thông &amp; Di chuyển</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B254" t="str">
-        <v>坐</v>
+        <v>不要</v>
       </c>
       <c r="C254" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7773,15 +7798,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I254" t="str">
-        <v>game.html?topic=chude12</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B255" t="str">
-        <v>大</v>
+        <v>不</v>
       </c>
       <c r="C255" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7802,15 +7827,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I255" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B256" t="str">
-        <v>对</v>
+        <v>的</v>
       </c>
       <c r="C256" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7831,15 +7856,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I256" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B257" t="str">
-        <v>多</v>
+        <v>都</v>
       </c>
       <c r="C257" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7860,15 +7885,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I257" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B258" t="str">
-        <v>非常</v>
+        <v>还</v>
       </c>
       <c r="C258" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7889,15 +7914,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I258" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B259" t="str">
-        <v>贵</v>
+        <v>和</v>
       </c>
       <c r="C259" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7918,15 +7943,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I259" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B260" t="str">
-        <v>好</v>
+        <v>很</v>
       </c>
       <c r="C260" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7947,15 +7972,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I260" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B261" t="str">
-        <v>好看</v>
+        <v>可以</v>
       </c>
       <c r="C261" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -7976,15 +8001,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I261" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B262" t="str">
-        <v>好听</v>
+        <v>了</v>
       </c>
       <c r="C262" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8005,15 +8030,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I262" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B263" t="str">
-        <v>好玩儿</v>
+        <v>吗</v>
       </c>
       <c r="C263" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8034,15 +8059,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I263" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B264" t="str">
-        <v>冷</v>
+        <v>没</v>
       </c>
       <c r="C264" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8063,15 +8088,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I264" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B265" t="str">
-        <v>忙</v>
+        <v>没关系</v>
       </c>
       <c r="C265" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8092,15 +8117,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I265" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B266" t="str">
-        <v>便宜</v>
+        <v>没事</v>
       </c>
       <c r="C266" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8121,15 +8146,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I266" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B267" t="str">
-        <v>漂亮</v>
+        <v>没有</v>
       </c>
       <c r="C267" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8150,15 +8175,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I267" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B268" t="str">
-        <v>热</v>
+        <v>哪个</v>
       </c>
       <c r="C268" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8179,15 +8204,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I268" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B269" t="str">
-        <v>少</v>
+        <v>哪些</v>
       </c>
       <c r="C269" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8208,15 +8233,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I269" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B270" t="str">
-        <v>小</v>
+        <v>那</v>
       </c>
       <c r="C270" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8237,15 +8262,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I270" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B271" t="str">
-        <v>新</v>
+        <v>那些</v>
       </c>
       <c r="C271" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8266,15 +8291,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I271" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Miêu tả &amp; Đánh giá</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B272" t="str">
-        <v>真</v>
+        <v>呢</v>
       </c>
       <c r="C272" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8295,15 +8320,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I272" t="str">
-        <v>game.html?topic=chude13</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B273" t="str">
-        <v>大学生</v>
+        <v>能</v>
       </c>
       <c r="C273" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8329,10 +8354,10 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B274" t="str">
-        <v>服务员</v>
+        <v>你好</v>
       </c>
       <c r="C274" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8358,10 +8383,10 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B275" t="str">
-        <v>工作</v>
+        <v>请</v>
       </c>
       <c r="C275" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8387,10 +8412,10 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B276" t="str">
-        <v>老师</v>
+        <v>什么</v>
       </c>
       <c r="C276" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8416,10 +8441,10 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B277" t="str">
-        <v>上班</v>
+        <v>是</v>
       </c>
       <c r="C277" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8445,10 +8470,10 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B278" t="str">
-        <v>上课</v>
+        <v>太</v>
       </c>
       <c r="C278" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8474,10 +8499,10 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B279" t="str">
-        <v>上学</v>
+        <v>喂</v>
       </c>
       <c r="C279" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8503,10 +8528,10 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B280" t="str">
-        <v>售货员</v>
+        <v>谢谢</v>
       </c>
       <c r="C280" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8532,10 +8557,10 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B281" t="str">
-        <v>下班</v>
+        <v>要</v>
       </c>
       <c r="C281" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8561,10 +8586,10 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B282" t="str">
-        <v>下课</v>
+        <v>也</v>
       </c>
       <c r="C282" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8590,10 +8615,10 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B283" t="str">
-        <v>小学生</v>
+        <v>再</v>
       </c>
       <c r="C283" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8619,10 +8644,10 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B284" t="str">
-        <v>学生</v>
+        <v>再见</v>
       </c>
       <c r="C284" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8648,10 +8673,10 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B285" t="str">
-        <v>医</v>
+        <v>在</v>
       </c>
       <c r="C285" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8677,10 +8702,10 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B286" t="str">
-        <v>医生</v>
+        <v>怎么</v>
       </c>
       <c r="C286" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8706,10 +8731,10 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Công việc &amp; Nghề nghiệp</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B287" t="str">
-        <v>中学生</v>
+        <v>怎么样</v>
       </c>
       <c r="C287" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8735,10 +8760,10 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B288" t="str">
-        <v>读</v>
+        <v>这</v>
       </c>
       <c r="C288" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8759,15 +8784,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I288" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B289" t="str">
-        <v>读书</v>
+        <v>这些</v>
       </c>
       <c r="C289" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8788,15 +8813,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I289" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
       <c r="B290" t="str">
-        <v>会</v>
+        <v>正在</v>
       </c>
       <c r="C290" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8817,15 +8842,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I290" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude14</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B291" t="str">
-        <v>见</v>
+        <v>狗</v>
       </c>
       <c r="C291" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8851,10 +8876,10 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B292" t="str">
-        <v>叫</v>
+        <v>猫</v>
       </c>
       <c r="C292" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8880,10 +8905,10 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B293" t="str">
-        <v>看</v>
+        <v>水</v>
       </c>
       <c r="C293" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8909,10 +8934,10 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B294" t="str">
-        <v>看见</v>
+        <v>天</v>
       </c>
       <c r="C294" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8938,10 +8963,10 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B295" t="str">
-        <v>请问</v>
+        <v>天气</v>
       </c>
       <c r="C295" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8967,10 +8992,10 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B296" t="str">
-        <v>认识</v>
+        <v>下雨</v>
       </c>
       <c r="C296" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -8996,10 +9021,10 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B297" t="str">
-        <v>说</v>
+        <v>雪</v>
       </c>
       <c r="C297" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9025,10 +9050,10 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B298" t="str">
-        <v>说话</v>
+        <v>雨</v>
       </c>
       <c r="C298" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9054,10 +9079,10 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Tự nhiên</v>
       </c>
       <c r="B299" t="str">
-        <v>听</v>
+        <v>早上</v>
       </c>
       <c r="C299" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9083,10 +9108,10 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B300" t="str">
-        <v>听见</v>
+        <v>包子</v>
       </c>
       <c r="C300" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9107,15 +9132,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I300" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B301" t="str">
-        <v>问</v>
+        <v>菜</v>
       </c>
       <c r="C301" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9136,15 +9161,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I301" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B302" t="str">
-        <v>问题</v>
+        <v>茶</v>
       </c>
       <c r="C302" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9165,15 +9190,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I302" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B303" t="str">
-        <v>想</v>
+        <v>饭</v>
       </c>
       <c r="C303" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9194,15 +9219,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I303" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B304" t="str">
-        <v>学</v>
+        <v>好吃</v>
       </c>
       <c r="C304" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9223,15 +9248,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I304" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B305" t="str">
-        <v>学习</v>
+        <v>鸡蛋</v>
       </c>
       <c r="C305" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9252,15 +9277,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I305" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Tư duy &amp; Nhận thức</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B306" t="str">
-        <v>知道</v>
+        <v>饺子</v>
       </c>
       <c r="C306" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9281,15 +9306,15 @@
         <v>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</v>
       </c>
       <c r="I306" t="str">
-        <v>game.html?topic=chude15</v>
+        <v>game.html?topic=chude16</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B307" t="str">
-        <v>狗</v>
+        <v>米饭</v>
       </c>
       <c r="C307" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9315,10 +9340,10 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B308" t="str">
-        <v>猫</v>
+        <v>面包</v>
       </c>
       <c r="C308" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9344,10 +9369,10 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B309" t="str">
-        <v>水</v>
+        <v>面条儿</v>
       </c>
       <c r="C309" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9373,10 +9398,10 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B310" t="str">
-        <v>天</v>
+        <v>牛奶</v>
       </c>
       <c r="C310" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9402,10 +9427,10 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B311" t="str">
-        <v>天气</v>
+        <v>苹果</v>
       </c>
       <c r="C311" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9431,10 +9456,10 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B312" t="str">
-        <v>下雨</v>
+        <v>水果</v>
       </c>
       <c r="C312" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9460,10 +9485,10 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B313" t="str">
-        <v>雪</v>
+        <v>晚饭</v>
       </c>
       <c r="C313" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9489,10 +9514,10 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B314" t="str">
-        <v>雨</v>
+        <v>午饭</v>
       </c>
       <c r="C314" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>
@@ -9518,10 +9543,10 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Tự nhiên</v>
+        <v>Đồ ăn &amp; Thức uống</v>
       </c>
       <c r="B315" t="str">
-        <v>早上</v>
+        <v>早饭</v>
       </c>
       <c r="C315" t="str">
         <v>Ai Là Triệu Phú HSK 2</v>

--- a/game_theo_chu_de.xlsx
+++ b/game_theo_chu_de.xlsx
@@ -1,30 +1,14 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>SheetJS</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>Game theo chủ đề</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="Game theo chủ đề" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"/>
-</file>
-
-<file path=xl\metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -46,7 +30,7 @@
 </metadata>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -91,7 +75,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -411,54 +395,34 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Game theo chủ đề" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I315"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="50.83203125" customWidth="1"/>
-    <col min="9" max="9" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Chủ đề</v>
       </c>
       <c r="B1" t="str">
-        <v xml:space="preserve">Những từ vựng sử dụng </v>
+        <v>Những từ vựng sử dụng</v>
       </c>
       <c r="C1" t="str">
-        <v>Tên Trò chơi (Trên Web)</v>
+        <v>Tên trò chơi</v>
       </c>
       <c r="D1" t="str">
-        <v>Công cụ Tạo Game</v>
+        <v>Công nghệ sử dụng</v>
       </c>
       <c r="E1" t="str">
-        <v>Loại GAME</v>
+        <v>Dạng trò chơi</v>
       </c>
       <c r="F1" t="str">
-        <v>Mục tiêu Sư phạm</v>
+        <v>Mục tiêu sư phạm</v>
       </c>
       <c r="G1" t="str">
-        <v>Gợi ý Ứng dụng</v>
+        <v>Cách thức sử dụng</v>
       </c>
       <c r="H1" t="str">
-        <v xml:space="preserve">Gợi ý Hoạt động </v>
+        <v>Tương tác</v>
       </c>
       <c r="I1" t="str">
         <v>LINK SẢN PHẨM (BẮT BUỘC)</v>
@@ -9572,134 +9536,134 @@
     </row>
   </sheetData>
   <mergeCells count="128">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I2:I5"/>
-    <mergeCell ref="A6:A40"/>
-    <mergeCell ref="C6:C40"/>
-    <mergeCell ref="D6:D40"/>
-    <mergeCell ref="E6:E40"/>
-    <mergeCell ref="F6:F40"/>
-    <mergeCell ref="G6:G40"/>
-    <mergeCell ref="H6:H40"/>
-    <mergeCell ref="I6:I40"/>
-    <mergeCell ref="A41:A77"/>
-    <mergeCell ref="C41:C77"/>
-    <mergeCell ref="D41:D77"/>
-    <mergeCell ref="E41:E77"/>
-    <mergeCell ref="F41:F77"/>
-    <mergeCell ref="G41:G77"/>
-    <mergeCell ref="H41:H77"/>
-    <mergeCell ref="I41:I77"/>
-    <mergeCell ref="A78:A116"/>
-    <mergeCell ref="C78:C116"/>
-    <mergeCell ref="D78:D116"/>
-    <mergeCell ref="E78:E116"/>
-    <mergeCell ref="F78:F116"/>
-    <mergeCell ref="G78:G116"/>
-    <mergeCell ref="H78:H116"/>
-    <mergeCell ref="I78:I116"/>
-    <mergeCell ref="A117:A142"/>
-    <mergeCell ref="C117:C142"/>
-    <mergeCell ref="D117:D142"/>
-    <mergeCell ref="E117:E142"/>
-    <mergeCell ref="F117:F142"/>
-    <mergeCell ref="G117:G142"/>
-    <mergeCell ref="H117:H142"/>
-    <mergeCell ref="I117:I142"/>
-    <mergeCell ref="A143:A158"/>
-    <mergeCell ref="C143:C158"/>
-    <mergeCell ref="D143:D158"/>
-    <mergeCell ref="E143:E158"/>
-    <mergeCell ref="F143:F158"/>
-    <mergeCell ref="G143:G158"/>
-    <mergeCell ref="H143:H158"/>
-    <mergeCell ref="I143:I158"/>
-    <mergeCell ref="A159:A178"/>
-    <mergeCell ref="C159:C178"/>
-    <mergeCell ref="D159:D178"/>
-    <mergeCell ref="E159:E178"/>
-    <mergeCell ref="F159:F178"/>
-    <mergeCell ref="G159:G178"/>
-    <mergeCell ref="H159:H178"/>
-    <mergeCell ref="I159:I178"/>
-    <mergeCell ref="A179:A192"/>
-    <mergeCell ref="C179:C192"/>
-    <mergeCell ref="D179:D192"/>
-    <mergeCell ref="E179:E192"/>
-    <mergeCell ref="F179:F192"/>
-    <mergeCell ref="G179:G192"/>
-    <mergeCell ref="H179:H192"/>
-    <mergeCell ref="I179:I192"/>
-    <mergeCell ref="A193:A197"/>
-    <mergeCell ref="C193:C197"/>
-    <mergeCell ref="D193:D197"/>
-    <mergeCell ref="E193:E197"/>
-    <mergeCell ref="F193:F197"/>
-    <mergeCell ref="G193:G197"/>
-    <mergeCell ref="H193:H197"/>
-    <mergeCell ref="I193:I197"/>
-    <mergeCell ref="A198:A217"/>
-    <mergeCell ref="C198:C217"/>
-    <mergeCell ref="D198:D217"/>
-    <mergeCell ref="E198:E217"/>
-    <mergeCell ref="F198:F217"/>
-    <mergeCell ref="G198:G217"/>
-    <mergeCell ref="H198:H217"/>
-    <mergeCell ref="I198:I217"/>
-    <mergeCell ref="A218:A244"/>
-    <mergeCell ref="C218:C244"/>
-    <mergeCell ref="D218:D244"/>
-    <mergeCell ref="E218:E244"/>
-    <mergeCell ref="F218:F244"/>
-    <mergeCell ref="G218:G244"/>
-    <mergeCell ref="H218:H244"/>
-    <mergeCell ref="I218:I244"/>
-    <mergeCell ref="A245:A254"/>
-    <mergeCell ref="C245:C254"/>
-    <mergeCell ref="D245:D254"/>
-    <mergeCell ref="E245:E254"/>
-    <mergeCell ref="F245:F254"/>
-    <mergeCell ref="G245:G254"/>
-    <mergeCell ref="H245:H254"/>
-    <mergeCell ref="I245:I254"/>
-    <mergeCell ref="A255:A272"/>
-    <mergeCell ref="C255:C272"/>
-    <mergeCell ref="D255:D272"/>
-    <mergeCell ref="E255:E272"/>
-    <mergeCell ref="F255:F272"/>
-    <mergeCell ref="G255:G272"/>
-    <mergeCell ref="H255:H272"/>
-    <mergeCell ref="I255:I272"/>
-    <mergeCell ref="A273:A287"/>
-    <mergeCell ref="C273:C287"/>
-    <mergeCell ref="D273:D287"/>
-    <mergeCell ref="E273:E287"/>
-    <mergeCell ref="F273:F287"/>
-    <mergeCell ref="G273:G287"/>
-    <mergeCell ref="H273:H287"/>
-    <mergeCell ref="I273:I287"/>
-    <mergeCell ref="A288:A306"/>
-    <mergeCell ref="C288:C306"/>
-    <mergeCell ref="D288:D306"/>
-    <mergeCell ref="E288:E306"/>
-    <mergeCell ref="F288:F306"/>
-    <mergeCell ref="G288:G306"/>
-    <mergeCell ref="H288:H306"/>
-    <mergeCell ref="I288:I306"/>
-    <mergeCell ref="A307:A315"/>
-    <mergeCell ref="C307:C315"/>
-    <mergeCell ref="D307:D315"/>
-    <mergeCell ref="E307:E315"/>
-    <mergeCell ref="F307:F315"/>
-    <mergeCell ref="G307:G315"/>
-    <mergeCell ref="H307:H315"/>
-    <mergeCell ref="I307:I315"/>
+    <mergeCell ref="A2:A38"/>
+    <mergeCell ref="C2:C38"/>
+    <mergeCell ref="D2:D38"/>
+    <mergeCell ref="E2:E38"/>
+    <mergeCell ref="F2:F38"/>
+    <mergeCell ref="G2:G38"/>
+    <mergeCell ref="H2:H38"/>
+    <mergeCell ref="I2:I38"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="F44:F47"/>
+    <mergeCell ref="G44:G47"/>
+    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="A48:A66"/>
+    <mergeCell ref="C48:C66"/>
+    <mergeCell ref="D48:D66"/>
+    <mergeCell ref="E48:E66"/>
+    <mergeCell ref="F48:F66"/>
+    <mergeCell ref="G48:G66"/>
+    <mergeCell ref="H48:H66"/>
+    <mergeCell ref="I48:I66"/>
+    <mergeCell ref="A67:A86"/>
+    <mergeCell ref="C67:C86"/>
+    <mergeCell ref="D67:D86"/>
+    <mergeCell ref="E67:E86"/>
+    <mergeCell ref="F67:F86"/>
+    <mergeCell ref="G67:G86"/>
+    <mergeCell ref="H67:H86"/>
+    <mergeCell ref="I67:I86"/>
+    <mergeCell ref="A87:A106"/>
+    <mergeCell ref="C87:C106"/>
+    <mergeCell ref="D87:D106"/>
+    <mergeCell ref="E87:E106"/>
+    <mergeCell ref="F87:F106"/>
+    <mergeCell ref="G87:G106"/>
+    <mergeCell ref="H87:H106"/>
+    <mergeCell ref="I87:I106"/>
+    <mergeCell ref="A107:A133"/>
+    <mergeCell ref="C107:C133"/>
+    <mergeCell ref="D107:D133"/>
+    <mergeCell ref="E107:E133"/>
+    <mergeCell ref="F107:F133"/>
+    <mergeCell ref="G107:G133"/>
+    <mergeCell ref="H107:H133"/>
+    <mergeCell ref="I107:I133"/>
+    <mergeCell ref="A134:A143"/>
+    <mergeCell ref="C134:C143"/>
+    <mergeCell ref="D134:D143"/>
+    <mergeCell ref="E134:E143"/>
+    <mergeCell ref="F134:F143"/>
+    <mergeCell ref="G134:G143"/>
+    <mergeCell ref="H134:H143"/>
+    <mergeCell ref="I134:I143"/>
+    <mergeCell ref="A144:A157"/>
+    <mergeCell ref="C144:C157"/>
+    <mergeCell ref="D144:D157"/>
+    <mergeCell ref="E144:E157"/>
+    <mergeCell ref="F144:F157"/>
+    <mergeCell ref="G144:G157"/>
+    <mergeCell ref="H144:H157"/>
+    <mergeCell ref="I144:I157"/>
+    <mergeCell ref="A158:A183"/>
+    <mergeCell ref="C158:C183"/>
+    <mergeCell ref="D158:D183"/>
+    <mergeCell ref="E158:E183"/>
+    <mergeCell ref="F158:F183"/>
+    <mergeCell ref="G158:G183"/>
+    <mergeCell ref="H158:H183"/>
+    <mergeCell ref="I158:I183"/>
+    <mergeCell ref="A184:A198"/>
+    <mergeCell ref="C184:C198"/>
+    <mergeCell ref="D184:D198"/>
+    <mergeCell ref="E184:E198"/>
+    <mergeCell ref="F184:F198"/>
+    <mergeCell ref="G184:G198"/>
+    <mergeCell ref="H184:H198"/>
+    <mergeCell ref="I184:I198"/>
+    <mergeCell ref="A199:A216"/>
+    <mergeCell ref="C199:C216"/>
+    <mergeCell ref="D199:D216"/>
+    <mergeCell ref="E199:E216"/>
+    <mergeCell ref="F199:F216"/>
+    <mergeCell ref="G199:G216"/>
+    <mergeCell ref="H199:H216"/>
+    <mergeCell ref="I199:I216"/>
+    <mergeCell ref="A217:A251"/>
+    <mergeCell ref="C217:C251"/>
+    <mergeCell ref="D217:D251"/>
+    <mergeCell ref="E217:E251"/>
+    <mergeCell ref="F217:F251"/>
+    <mergeCell ref="G217:G251"/>
+    <mergeCell ref="H217:H251"/>
+    <mergeCell ref="I217:I251"/>
+    <mergeCell ref="A252:A290"/>
+    <mergeCell ref="C252:C290"/>
+    <mergeCell ref="D252:D290"/>
+    <mergeCell ref="E252:E290"/>
+    <mergeCell ref="F252:F290"/>
+    <mergeCell ref="G252:G290"/>
+    <mergeCell ref="H252:H290"/>
+    <mergeCell ref="I252:I290"/>
+    <mergeCell ref="A291:A299"/>
+    <mergeCell ref="C291:C299"/>
+    <mergeCell ref="D291:D299"/>
+    <mergeCell ref="E291:E299"/>
+    <mergeCell ref="F291:F299"/>
+    <mergeCell ref="G291:G299"/>
+    <mergeCell ref="H291:H299"/>
+    <mergeCell ref="I291:I299"/>
+    <mergeCell ref="A300:A315"/>
+    <mergeCell ref="C300:C315"/>
+    <mergeCell ref="D300:D315"/>
+    <mergeCell ref="E300:E315"/>
+    <mergeCell ref="F300:F315"/>
+    <mergeCell ref="G300:G315"/>
+    <mergeCell ref="H300:H315"/>
+    <mergeCell ref="I300:I315"/>
   </mergeCells>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I315"/>

--- a/game_theo_chu_de.xlsx
+++ b/game_theo_chu_de.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BRAVO 15\Downloads\game tieng trung hsk 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482C19DC-E1D5-4628-8485-143E0C9E3BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5A21F4-CA0B-4230-B15A-A11636339471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HSK 2 Topics Used" sheetId="1" r:id="rId1"/>
+    <sheet name="Game theo chủ đề" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="53">
   <si>
     <t>Chủ đề</t>
   </si>
@@ -28,28 +28,324 @@
     <t>Những từ vựng sử dụng</t>
   </si>
   <si>
-    <t>Tên trò chơi</t>
-  </si>
-  <si>
-    <t>Công nghệ sử dụng</t>
-  </si>
-  <si>
-    <t>Dạng trò chơi</t>
-  </si>
-  <si>
-    <t>Mục tiêu sư phạm</t>
-  </si>
-  <si>
-    <t>Cách thức sử dụng</t>
-  </si>
-  <si>
-    <t>Tương tác</t>
+    <t>Tên Trò chơi (Trên Web)</t>
+  </si>
+  <si>
+    <t>Công cụ Tạo Game</t>
+  </si>
+  <si>
+    <t>TV Phụ trách</t>
+  </si>
+  <si>
+    <t>Loại GAME</t>
   </si>
   <si>
     <t>LINK SẢN PHẨM (BẮT BUỘC)</t>
   </si>
   <si>
+    <t>Mục tiêu Sư phạm</t>
+  </si>
+  <si>
+    <t>Gợi ý Ứng dụng</t>
+  </si>
+  <si>
+    <t>Gợi ý Hoạt động</t>
+  </si>
+  <si>
+    <t>Con người &amp; Các mối quan hệ</t>
+  </si>
+  <si>
+    <t>Ai Là Triệu Phú HSK 2</t>
+  </si>
+  <si>
+    <t>HTML, CSS, Javascript</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Trắc nghiệm / Trò chơi truyền hình</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude1</t>
+  </si>
+  <si>
+    <t>Nhận diện Hán tự, Ghi nhớ nghĩa, Phản xạ từ vựng HSK 2</t>
+  </si>
+  <si>
+    <t>Khởi động 5 phút đầu giờ; Bài tập về nhà; Ôn tập cuối chương</t>
+  </si>
+  <si>
+    <t>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</t>
+  </si>
+  <si>
+    <t>Cơ thể &amp; Sức khỏe</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude2</t>
+  </si>
+  <si>
+    <t>Cảm xúc &amp; Thái độ</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude3</t>
+  </si>
+  <si>
+    <t>Đời sống sinh hoạt</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude4</t>
+  </si>
+  <si>
+    <t>Đồ vật &amp; Công cụ</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude5</t>
+  </si>
+  <si>
+    <t>Địa điểm &amp; Nơi chốn</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude6</t>
+  </si>
+  <si>
+    <t>Giao thông &amp; Di chuyển</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude7</t>
+  </si>
+  <si>
+    <t>Không gian &amp; Vị trí</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude8</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude9</t>
+  </si>
+  <si>
+    <t>Miêu tả &amp; Đánh giá</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude10</t>
+  </si>
+  <si>
     <t>Công cụ ngữ pháp &amp; Cấu trúc</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude11</t>
+  </si>
+  <si>
+    <t>Tự nhiên</t>
+  </si>
+  <si>
+    <t>game.html?topic=chude12</t>
+  </si>
+  <si>
+    <t>介绍
+奶奶
+男孩儿
+女孩儿
+妻子
+小孩儿
+姓
+姓名
+爷爷
+丈夫</t>
+  </si>
+  <si>
+    <t>白色
+帮
+长
+高
+个子
+介绍
+累
+身体
+手
+手表
+疼
+头
+眼睛
+药
+药店</t>
+  </si>
+  <si>
+    <t>啊
+爱好
+不错
+不好意思
+坏
+快乐
+没意思
+舒服
+希望
+笑</t>
+  </si>
+  <si>
+    <t>爱情片
+帮忙
+包
+笔
+打
+打开
+蛋糕
+等
+点
+告诉
+画
+教
+开学
+考
+考试
+旅游
+拿
+跑步
+肉
+试
+送
+踢
+跳舞
+洗
+游
+游泳
+运动
+站
+准备
+花</t>
+  </si>
+  <si>
+    <t>包
+本子
+笔
+床
+蛋糕
+花
+画
+画笔
+机票
+咖啡
+裤子
+篮球
+礼物
+门
+门票
+面
+奶茶
+票
+球
+书包
+足球</t>
+  </si>
+  <si>
+    <t>班
+车站
+饭馆
+房子
+高中
+机场
+教室
+酒店
+楼
+路
+路上
+门口
+商场
+外国
+洗手间
+药店
+站</t>
+  </si>
+  <si>
+    <t>出国
+出门
+出去
+打车
+地铁
+动
+飞
+公交车
+过
+过来
+过去
+回来
+回去
+接
+进
+进来
+进去
+离
+路上
+跑
+跑步
+上来
+上去
+上网
+往
+下来
+下去
+站
+走
+走路
+出</t>
+  </si>
+  <si>
+    <t>出去
+后面
+近
+里面
+门口
+旁边
+前面
+上面
+外面
+网上
+下面
+右
+右边
+远
+左</t>
+  </si>
+  <si>
+    <t>从小
+过年
+经常
+就
+开始
+开学
+快要
+生日
+时
+小时候
+新年
+一会儿
+已经
+有时
+周</t>
+  </si>
+  <si>
+    <t>白色
+不错
+长
+错
+高
+好像
+黑色
+红色
+坏
+近
+快
+慢
+没意思
+晴
+完
+颜色
+阴
+有意思
+远</t>
   </si>
   <si>
     <t>啊
@@ -95,293 +391,6 @@
 最</t>
   </si>
   <si>
-    <t>Ai Là Triệu Phú HSK 2</t>
-  </si>
-  <si>
-    <t>HTML, CSS, Javascript</t>
-  </si>
-  <si>
-    <t>Trắc nghiệm / Trò chơi truyền hình</t>
-  </si>
-  <si>
-    <t>Nhận diện Hán tự, Ghi nhớ nghĩa, Phản xạ từ vựng HSK 2</t>
-  </si>
-  <si>
-    <t>Khởi động 5 phút đầu giờ; Bài tập về nhà; Ôn tập cuối chương</t>
-  </si>
-  <si>
-    <t>Cá nhân, Chia đội thi đấu (Đội nào giành được nhiều tiền hơn), Giáo viên chiếu bảng lớp học</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude1</t>
-  </si>
-  <si>
-    <t>Cảm xúc &amp; Thái độ</t>
-  </si>
-  <si>
-    <t>啊
-爱好
-不错
-不好意思
-坏
-快乐
-没意思
-舒服
-希望
-笑</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude2</t>
-  </si>
-  <si>
-    <t>Đời sống sinh hoạt</t>
-  </si>
-  <si>
-    <t>爱情片
-帮忙
-包
-笔
-打
-打开
-蛋糕
-等
-点
-告诉
-画
-教
-开学
-考
-考试
-旅游
-拿
-跑步
-肉
-试
-送
-踢
-跳舞
-洗
-游
-游泳
-运动
-站
-准备
-花</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude3</t>
-  </si>
-  <si>
-    <t>Miêu tả &amp; Đánh giá</t>
-  </si>
-  <si>
-    <t>白色
-不错
-长
-错
-高
-好像
-黑色
-红色
-坏
-近
-快
-慢
-没意思
-晴
-完
-颜色
-阴
-有意思
-远</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude4</t>
-  </si>
-  <si>
-    <t>Cơ thể &amp; Sức khỏe</t>
-  </si>
-  <si>
-    <t>白色
-帮
-长
-高
-个子
-介绍
-累
-身体
-手
-手表
-疼
-头
-眼睛
-药
-药店</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude5</t>
-  </si>
-  <si>
-    <t>Địa điểm &amp; Nơi chốn</t>
-  </si>
-  <si>
-    <t>班
-车站
-饭馆
-房子
-高中
-机场
-教室
-酒店
-楼
-路
-路上
-门口
-商场
-外国
-洗手间
-药店
-站</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude6</t>
-  </si>
-  <si>
-    <t>Đồ vật &amp; Công cụ</t>
-  </si>
-  <si>
-    <t>包
-本子
-笔
-床
-蛋糕
-花
-画
-画笔
-机票
-咖啡
-裤子
-篮球
-礼物
-门
-门票
-面
-奶茶
-票
-球
-书包
-足球</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude7</t>
-  </si>
-  <si>
-    <t>Giao thông &amp; Di chuyển</t>
-  </si>
-  <si>
-    <t>出国
-出门
-出去
-打车
-地铁
-动
-飞
-公交车
-过
-过来
-过去
-回来
-回去
-接
-进
-进来
-进去
-离
-路上
-跑
-跑步
-上来
-上去
-上网
-往
-下来
-下去
-站
-走
-走路
-出</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude8</t>
-  </si>
-  <si>
-    <t>Không gian &amp; Vị trí</t>
-  </si>
-  <si>
-    <t>出去
-后面
-近
-里面
-门口
-旁边
-前面
-上面
-外面
-网上
-下面
-右
-右边
-远
-左</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude9</t>
-  </si>
-  <si>
-    <t>Thời gian</t>
-  </si>
-  <si>
-    <t>从小
-过年
-经常
-就
-开始
-开学
-快要
-生日
-时
-小时候
-新年
-一会儿
-已经
-有时
-周</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude10</t>
-  </si>
-  <si>
-    <t>Con người &amp; Các mối quan hệ</t>
-  </si>
-  <si>
-    <t>介绍
-奶奶
-男孩儿
-女孩儿
-妻子
-小孩儿
-姓
-姓名
-爷爷
-丈夫</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude11</t>
-  </si>
-  <si>
-    <t>Tự nhiên</t>
-  </si>
-  <si>
     <t>咖啡
 绿色
 鸟
@@ -391,9 +400,6 @@
 鱼
 红茶
 绿茶</t>
-  </si>
-  <si>
-    <t>game.html?topic=chude12</t>
   </si>
 </sst>
 </file>
@@ -773,19 +779,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.796875" customWidth="1"/>
     <col min="2" max="2" width="50.796875" customWidth="1"/>
-    <col min="3" max="3" width="30.796875" customWidth="1"/>
-    <col min="4" max="4" width="20.796875" customWidth="1"/>
-    <col min="5" max="5" width="30.796875" customWidth="1"/>
-    <col min="6" max="8" width="50.796875" customWidth="1"/>
-    <col min="9" max="9" width="30.796875" customWidth="1"/>
+    <col min="3" max="3" width="25.796875" customWidth="1"/>
+    <col min="4" max="5" width="20.796875" customWidth="1"/>
+    <col min="6" max="7" width="30.796875" customWidth="1"/>
+    <col min="8" max="8" width="50.796875" customWidth="1"/>
+    <col min="9" max="10" width="60.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -813,13 +819,16 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="156" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -842,13 +851,16 @@
       <c r="I2" t="s">
         <v>17</v>
       </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="156" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="234" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -863,21 +875,24 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="156" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -892,21 +907,24 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="296.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -921,21 +939,24 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="234" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="327.60000000000002" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -950,21 +971,24 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="265.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="265.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -979,21 +1003,24 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="327.60000000000002" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -1008,21 +1035,24 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="234" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -1037,21 +1067,24 @@
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="234" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="234" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -1066,21 +1099,24 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="234" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="296.39999999999998" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -1095,21 +1131,24 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="156" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -1124,21 +1163,24 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>17</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -1153,19 +1195,23 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>17</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I1 A13 A2 C2:I2 A3 C3:I3 A4 C4:I4 A5 C5:I5 A6 C6:I6 A7 C7:I7 A8 C8:I8 A9 C9:I9 A10 C10:I10 A11 C11:I11 A12 C12:I12 C13:I13" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A13 A2 C2:J2 A3 C3:J3 A4 C4:J4 A5 C5:J5 A6 C6:J6 A7 C7:J7 A8 C8:J8 A9 C9:J9 A10 C10:J10 A11 C11:J11 A12 C12:J12 C13:J13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>